--- a/data_cruda/DFEDTARU.xlsx
+++ b/data_cruda/DFEDTARU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ANTHONY\Documents\ANTHONY\Investigación\Artículos\Tope_tasas_interés_18_09_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C14C662-B3BD-410C-8A1D-0B72946FC476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC587A9-D051-4435-9085-CDD2E2092EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -44,13 +44,13 @@
     <t>DFEDTARU</t>
   </si>
   <si>
-    <t>Federal Funds Target Range - Upper Limit, Percent, Monthly, Not Seasonally Adjusted</t>
-  </si>
-  <si>
     <t>Data Updated: 2026-09-20</t>
   </si>
   <si>
     <t>observation_date</t>
+  </si>
+  <si>
+    <t>Federal Funds Target Range - Upper Limit, Percent, Monthly, Not Seasonally Adjusted,End of Period</t>
   </si>
 </sst>
 </file>
@@ -469,10 +469,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
         <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -491,7 +491,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>6</v>
